--- a/212-corriger-interopsanteorg/ig/StructureDefinition-as-ext-lieu-dit.xlsx
+++ b/212-corriger-interopsanteorg/ig/StructureDefinition-as-ext-lieu-dit.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-07-01T16:13:56+00:00</t>
+    <t>2024-07-01T16:18:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
